--- a/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
@@ -479,7 +479,7 @@
         <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>4570</v>
+        <v>4558</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="G5" t="n">
         <v>1244.92</v>
@@ -703,7 +703,7 @@
         <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>15059</v>
+        <v>15040</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>4589</v>
+        <v>4581</v>
       </c>
       <c r="G11" t="n">
         <v>10167.8</v>
@@ -787,7 +787,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         <v>95</v>
       </c>
       <c r="F15" t="n">
-        <v>36071</v>
+        <v>36030</v>
       </c>
       <c r="G15" t="n">
         <v>2117.8</v>
@@ -955,7 +955,7 @@
         <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>810</v>
+        <v>777</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>2089</v>
+        <v>2085</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>28</v>
       </c>
       <c r="F35" t="n">
-        <v>1727</v>
+        <v>1720</v>
       </c>
       <c r="G35" t="n">
         <v>8466.1</v>
@@ -1459,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G38" t="n">
         <v>1270.34</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>34</v>
       </c>
       <c r="F49" t="n">
-        <v>3715</v>
+        <v>3690</v>
       </c>
       <c r="G49" t="n">
         <v>6270.34</v>
@@ -1823,7 +1823,7 @@
         <v>13</v>
       </c>
       <c r="F50" t="n">
-        <v>2337</v>
+        <v>2324</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>23</v>
       </c>
       <c r="F51" t="n">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>5668</v>
+        <v>5660</v>
       </c>
       <c r="G55" t="n">
         <v>1651.69</v>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v>17</v>
       </c>
       <c r="F59" t="n">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="F60" t="n">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>14</v>
       </c>
       <c r="F61" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>5106</v>
+        <v>5105</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2327,7 +2327,7 @@
         <v>65</v>
       </c>
       <c r="F68" t="n">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="G68" t="n">
         <v>5083.9</v>
@@ -2467,7 +2467,7 @@
         <v>5</v>
       </c>
       <c r="F73" t="n">
-        <v>1569</v>
+        <v>1545</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="F74" t="n">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>115</v>
       </c>
       <c r="F80" t="n">
-        <v>31778</v>
+        <v>31754</v>
       </c>
       <c r="G80" t="n">
         <v>2117.8</v>
@@ -2691,7 +2691,7 @@
         <v>39</v>
       </c>
       <c r="F81" t="n">
-        <v>3309</v>
+        <v>3304</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>41</v>
       </c>
       <c r="F82" t="n">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>984</v>
+        <v>930</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3475,7 +3475,7 @@
         <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>7</v>
       </c>
       <c r="F110" t="n">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>22</v>
       </c>
       <c r="F111" t="n">
-        <v>4206</v>
+        <v>4187</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>4</v>
       </c>
       <c r="F112" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G112" t="n">
         <v>8466.1</v>
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         <v>4</v>
       </c>
       <c r="F118" t="n">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>13</v>
       </c>
       <c r="F120" t="n">
-        <v>3871</v>
+        <v>3841</v>
       </c>
       <c r="G120" t="n">
         <v>1651.69</v>
@@ -3839,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>2277</v>
+        <v>2188</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
         <v>3</v>
       </c>
       <c r="F129" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4959,7 +4959,7 @@
         <v>4</v>
       </c>
       <c r="F162" t="n">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         <v>14</v>
       </c>
       <c r="F163" t="n">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
         <v>43</v>
       </c>
       <c r="F168" t="n">
-        <v>5499</v>
+        <v>5487</v>
       </c>
       <c r="G168" t="n">
         <v>2880.51</v>
@@ -5239,7 +5239,7 @@
         <v>16</v>
       </c>
       <c r="F172" t="n">
-        <v>2739</v>
+        <v>2734</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
         <v>60</v>
       </c>
       <c r="F173" t="n">
-        <v>12615</v>
+        <v>12614</v>
       </c>
       <c r="G173" t="n">
         <v>5083.9</v>
@@ -5351,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="F176" t="n">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5379,7 +5379,7 @@
         <v>22</v>
       </c>
       <c r="F177" t="n">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5491,7 +5491,7 @@
         <v>22</v>
       </c>
       <c r="F181" t="n">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="G181" t="n">
         <v>2356.2</v>
@@ -5519,7 +5519,7 @@
         <v>2</v>
       </c>
       <c r="F182" t="n">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5819,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -6302,28 +6302,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>752</v>
+        <v>2714</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>49.99333333333333</v>
+        <v>487.28</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -6335,22 +6335,22 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>752</v>
+        <v>402</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>49.99333333333333</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -6368,22 +6368,22 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>752</v>
+        <v>1147</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>49.99333333333333</v>
+        <v>163.61</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -6401,28 +6401,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2714</v>
+        <v>6405</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F18" t="n">
-        <v>487.28</v>
+        <v>632.1799999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -6434,22 +6434,22 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>406</v>
+        <v>800</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>72.68000000000001</v>
+        <v>624.28</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -6467,22 +6467,22 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>523</v>
+        <v>6815</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F20" t="n">
-        <v>48.36666666666667</v>
+        <v>505.09</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -6500,28 +6500,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>523</v>
+        <v>10653</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F21" t="n">
-        <v>48.36666666666667</v>
+        <v>1207.89</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -6533,22 +6533,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>523</v>
+        <v>4604</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>48.36666666666667</v>
+        <v>500.75</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>804</v>
+        <v>6042</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F23" t="n">
-        <v>146.21</v>
+        <v>695.35</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -6599,22 +6599,22 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1150</v>
+        <v>4382</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F24" t="n">
-        <v>163.61</v>
+        <v>531.59</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -6632,22 +6632,22 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6405</v>
+        <v>3769</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" t="n">
-        <v>632.1799999999999</v>
+        <v>505.11</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -6665,22 +6665,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>800</v>
+        <v>1969</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
-        <v>624.28</v>
+        <v>256.53</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -6698,28 +6698,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>283</v>
+        <v>2084</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>111.61</v>
+        <v>176.35</v>
       </c>
       <c r="G27" t="n">
-        <v>3219.49</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -6731,28 +6731,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6815</v>
+        <v>3464</v>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="F28" t="n">
-        <v>505.09</v>
+        <v>877.91</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>6270.34</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -6764,28 +6764,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10653</v>
+        <v>930</v>
       </c>
       <c r="E29" t="n">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="F29" t="n">
-        <v>1207.89</v>
+        <v>755.98</v>
       </c>
       <c r="G29" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -6797,22 +6797,22 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4604</v>
+        <v>930</v>
       </c>
       <c r="E30" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F30" t="n">
-        <v>500.75</v>
+        <v>755.98</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -6830,22 +6830,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6042</v>
+        <v>930</v>
       </c>
       <c r="E31" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F31" t="n">
-        <v>695.35</v>
+        <v>755.98</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6863,22 +6863,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4382</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>531.59</v>
+        <v>4.29</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -6896,22 +6896,22 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3774</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>505.11</v>
+        <v>4.29</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6929,22 +6929,22 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1974</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>256.53</v>
+        <v>4.29</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -6962,22 +6962,22 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2114</v>
+        <v>111</v>
       </c>
       <c r="E35" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>176.35</v>
+        <v>29.81666666666667</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -6995,22 +6995,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1185</v>
+        <v>111</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>47.24</v>
+        <v>29.81666666666667</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -7028,22 +7028,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1185</v>
+        <v>111</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>47.24</v>
+        <v>29.81666666666667</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -7061,22 +7061,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1185</v>
+        <v>4498</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>47.24</v>
+        <v>428.66</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -7094,28 +7094,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3468</v>
+        <v>2131</v>
       </c>
       <c r="E39" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
-        <v>877.91</v>
+        <v>319.46</v>
       </c>
       <c r="G39" t="n">
-        <v>6270.34</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -7127,22 +7127,22 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>930</v>
+        <v>82</v>
       </c>
       <c r="E40" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>755.98</v>
+        <v>9.85</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -7151,369 +7151,6 @@
         <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>930</v>
-      </c>
-      <c r="E41" t="n">
-        <v>57</v>
-      </c>
-      <c r="F41" t="n">
-        <v>755.98</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>930</v>
-      </c>
-      <c r="E42" t="n">
-        <v>57</v>
-      </c>
-      <c r="F42" t="n">
-        <v>755.98</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>B0CDPP45BM</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>5</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>5</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>111</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" t="n">
-        <v>29.81666666666667</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>111</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" t="n">
-        <v>29.81666666666667</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>111</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2</v>
-      </c>
-      <c r="F48" t="n">
-        <v>29.81666666666667</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4498</v>
-      </c>
-      <c r="E49" t="n">
-        <v>40</v>
-      </c>
-      <c r="F49" t="n">
-        <v>428.66</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>2131</v>
-      </c>
-      <c r="E50" t="n">
-        <v>26</v>
-      </c>
-      <c r="F50" t="n">
-        <v>319.46</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>82</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
@@ -986,10 +986,10 @@
         <v>3063</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>11863.56</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -5819,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6302,28 +6302,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2714</v>
+        <v>752</v>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>487.28</v>
+        <v>49.99333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -6335,22 +6335,22 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>402</v>
+        <v>752</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>72.68000000000001</v>
+        <v>49.99333333333333</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -6368,22 +6368,22 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1147</v>
+        <v>752</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>163.61</v>
+        <v>49.99333333333333</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -6401,28 +6401,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6405</v>
+        <v>2714</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
-        <v>632.1799999999999</v>
+        <v>487.28</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -6434,22 +6434,22 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>800</v>
+        <v>402</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>624.28</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -6467,22 +6467,22 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6815</v>
+        <v>523</v>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>505.09</v>
+        <v>48.36666666666667</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -6500,28 +6500,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10653</v>
+        <v>523</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>1207.89</v>
+        <v>48.36666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -6533,22 +6533,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4604</v>
+        <v>523</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>500.75</v>
+        <v>48.36666666666667</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6042</v>
+        <v>804</v>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>695.35</v>
+        <v>146.21</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -6599,22 +6599,22 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4382</v>
+        <v>1147</v>
       </c>
       <c r="E24" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>531.59</v>
+        <v>163.61</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -6632,22 +6632,22 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3769</v>
+        <v>6405</v>
       </c>
       <c r="E25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
-        <v>505.11</v>
+        <v>632.1799999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -6665,22 +6665,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1969</v>
+        <v>800</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F26" t="n">
-        <v>256.53</v>
+        <v>624.28</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -6698,28 +6698,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2084</v>
+        <v>283</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>176.35</v>
+        <v>111.61</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3219.49</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -6731,28 +6731,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3464</v>
+        <v>6815</v>
       </c>
       <c r="E28" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="F28" t="n">
-        <v>877.91</v>
+        <v>505.09</v>
       </c>
       <c r="G28" t="n">
-        <v>6270.34</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -6764,28 +6764,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>930</v>
+        <v>10653</v>
       </c>
       <c r="E29" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="F29" t="n">
-        <v>755.98</v>
+        <v>1207.89</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -6797,22 +6797,22 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>930</v>
+        <v>4604</v>
       </c>
       <c r="E30" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F30" t="n">
-        <v>755.98</v>
+        <v>500.75</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -6830,22 +6830,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>930</v>
+        <v>6042</v>
       </c>
       <c r="E31" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F31" t="n">
-        <v>755.98</v>
+        <v>695.35</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6863,22 +6863,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4382</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="F32" t="n">
-        <v>4.29</v>
+        <v>531.59</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -6896,22 +6896,22 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>3769</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="F33" t="n">
-        <v>4.29</v>
+        <v>505.11</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6929,22 +6929,22 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>1969</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F34" t="n">
-        <v>4.29</v>
+        <v>256.53</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -6962,22 +6962,22 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>111</v>
+        <v>2084</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F35" t="n">
-        <v>29.81666666666667</v>
+        <v>176.35</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -6995,22 +6995,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>111</v>
+        <v>1185</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>29.81666666666667</v>
+        <v>47.24</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -7028,22 +7028,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>111</v>
+        <v>1185</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
-        <v>29.81666666666667</v>
+        <v>47.24</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -7061,22 +7061,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4498</v>
+        <v>1185</v>
       </c>
       <c r="E38" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>428.66</v>
+        <v>47.24</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -7094,28 +7094,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2131</v>
+        <v>3464</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="F39" t="n">
-        <v>319.46</v>
+        <v>877.91</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>6270.34</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -7127,30 +7127,393 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>930</v>
+      </c>
+      <c r="E40" t="n">
+        <v>57</v>
+      </c>
+      <c r="F40" t="n">
+        <v>755.98</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>930</v>
+      </c>
+      <c r="E41" t="n">
+        <v>57</v>
+      </c>
+      <c r="F41" t="n">
+        <v>755.98</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>930</v>
+      </c>
+      <c r="E42" t="n">
+        <v>57</v>
+      </c>
+      <c r="F42" t="n">
+        <v>755.98</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>111</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>29.81666666666667</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>111</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>29.81666666666667</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>111</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>29.81666666666667</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4498</v>
+      </c>
+      <c r="E49" t="n">
+        <v>40</v>
+      </c>
+      <c r="F49" t="n">
+        <v>428.66</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2131</v>
+      </c>
+      <c r="E50" t="n">
+        <v>26</v>
+      </c>
+      <c r="F50" t="n">
+        <v>319.46</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D51" t="n">
         <v>82</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E51" t="n">
         <v>1</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F51" t="n">
         <v>9.85</v>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="G5" t="n">
         <v>1244.92</v>
@@ -5819,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6212,19 +6212,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4762</v>
+        <v>1587</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>812.61</v>
+        <v>270.87</v>
       </c>
       <c r="G12" t="n">
-        <v>2856.19</v>
+        <v>952.0633333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -6236,28 +6236,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>304</v>
+        <v>1587</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>33.07102778356614</v>
+        <v>270.87</v>
       </c>
       <c r="G13" t="n">
-        <v>1046.67</v>
+        <v>952.0633333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -6269,28 +6269,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1385</v>
+        <v>1587</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>150.3989722164339</v>
+        <v>270.87</v>
       </c>
       <c r="G14" t="n">
-        <v>4760</v>
+        <v>952.0633333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -6302,28 +6302,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>752</v>
+        <v>563</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>49.99333333333333</v>
+        <v>61.15666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1935.556666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -6335,28 +6335,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>752</v>
+        <v>563</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>49.99333333333333</v>
+        <v>61.15666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1935.556666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -6368,28 +6368,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>752</v>
+        <v>563</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>49.99333333333333</v>
+        <v>61.15666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1935.556666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -6401,28 +6401,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2714</v>
+        <v>2257</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>487.28</v>
+        <v>149.98</v>
       </c>
       <c r="G18" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6443,19 +6443,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>402</v>
+        <v>2714</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
-        <v>72.68000000000001</v>
+        <v>487.28</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>523</v>
+        <v>402</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>48.36666666666667</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -6505,17 +6505,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>523</v>
+        <v>1568</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>48.36666666666667</v>
+        <v>145.1</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -6533,22 +6533,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>523</v>
+        <v>804</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>48.36666666666667</v>
+        <v>146.21</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>804</v>
+        <v>1147</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>146.21</v>
+        <v>163.61</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -6599,7 +6599,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1147</v>
+        <v>6405</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F24" t="n">
-        <v>163.61</v>
+        <v>632.1799999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -6632,7 +6632,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6641,13 +6641,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6405</v>
+        <v>800</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>632.1799999999999</v>
+        <v>624.28</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -6665,28 +6665,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>800</v>
+        <v>283</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>624.28</v>
+        <v>111.61</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3219.49</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -6698,28 +6698,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>283</v>
+        <v>6815</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>111.61</v>
+        <v>505.09</v>
       </c>
       <c r="G27" t="n">
-        <v>3219.49</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6740,19 +6740,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6815</v>
+        <v>10653</v>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="F28" t="n">
-        <v>505.09</v>
+        <v>1207.89</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6773,19 +6773,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10653</v>
+        <v>4604</v>
       </c>
       <c r="E29" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="F29" t="n">
-        <v>1207.89</v>
+        <v>500.75</v>
       </c>
       <c r="G29" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4604</v>
+        <v>6042</v>
       </c>
       <c r="E30" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F30" t="n">
-        <v>500.75</v>
+        <v>695.35</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -6830,7 +6830,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6042</v>
+        <v>4382</v>
       </c>
       <c r="E31" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F31" t="n">
-        <v>695.35</v>
+        <v>531.59</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6863,7 +6863,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6872,13 +6872,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4382</v>
+        <v>3769</v>
       </c>
       <c r="E32" t="n">
         <v>46</v>
       </c>
       <c r="F32" t="n">
-        <v>531.59</v>
+        <v>505.11</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -6896,7 +6896,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6905,13 +6905,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3769</v>
+        <v>1969</v>
       </c>
       <c r="E33" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F33" t="n">
-        <v>505.11</v>
+        <v>256.53</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6938,13 +6938,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1969</v>
+        <v>2084</v>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F34" t="n">
-        <v>256.53</v>
+        <v>176.35</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -6962,22 +6962,22 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2084</v>
+        <v>3556</v>
       </c>
       <c r="E35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>176.35</v>
+        <v>141.72</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -6995,7 +6995,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7004,16 +7004,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1185</v>
+        <v>1155</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F36" t="n">
-        <v>47.24</v>
+        <v>292.6366666666667</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2090.113333333333</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -7028,25 +7028,25 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1185</v>
+        <v>1155</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F37" t="n">
-        <v>47.24</v>
+        <v>292.6366666666667</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2090.113333333333</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -7061,7 +7061,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7070,16 +7070,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1185</v>
+        <v>1155</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F38" t="n">
-        <v>47.24</v>
+        <v>292.6366666666667</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2090.113333333333</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -7094,28 +7094,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3464</v>
+        <v>930</v>
       </c>
       <c r="E39" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F39" t="n">
-        <v>877.91</v>
+        <v>755.98</v>
       </c>
       <c r="G39" t="n">
-        <v>6270.34</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -7193,22 +7193,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>930</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>755.98</v>
+        <v>4.29</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -7292,22 +7292,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>111</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>4.29</v>
+        <v>29.81666666666667</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -7391,22 +7391,22 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>111</v>
+        <v>4498</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F48" t="n">
-        <v>29.81666666666667</v>
+        <v>428.66</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -7424,7 +7424,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7433,13 +7433,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4498</v>
+        <v>2131</v>
       </c>
       <c r="E49" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
-        <v>428.66</v>
+        <v>319.46</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2131</v>
+        <v>82</v>
       </c>
       <c r="E50" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>319.46</v>
+        <v>9.85</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -7481,39 +7481,6 @@
         <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>82</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
@@ -3618,10 +3618,10 @@
         <v>276348</v>
       </c>
       <c r="G114" t="n">
-        <v>5168.64</v>
+        <v>10464.4</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -8619,7 +8619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8678,23 +8678,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2344</v>
+        <v>7640</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="F2" t="n">
-        <v>467.1204429276933</v>
+        <v>1522.8</v>
       </c>
       <c r="G2" t="n">
-        <v>2549.15</v>
+        <v>8310.16</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -8706,28 +8706,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - BM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5296</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1055.679557072307</v>
+        <v>19.89</v>
       </c>
       <c r="G3" t="n">
-        <v>5761.01</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -8805,22 +8805,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - BM</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - Exact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>19.89</v>
+        <v>13.27666666666667</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -8904,22 +8904,22 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>217</v>
+        <v>893</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>13.27666666666667</v>
+        <v>156.2766666666667</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -9003,25 +9003,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>893</v>
+        <v>14556</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
-        <v>156.2766666666667</v>
+        <v>1595.696666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3954.52</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -9045,19 +9045,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43667</v>
+        <v>14556</v>
       </c>
       <c r="E13" t="n">
-        <v>430</v>
+        <v>143</v>
       </c>
       <c r="F13" t="n">
-        <v>4787.09</v>
+        <v>1595.696666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>11863.56</v>
+        <v>3954.52</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -9069,28 +9069,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33371</v>
+        <v>14556</v>
       </c>
       <c r="E14" t="n">
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="F14" t="n">
-        <v>3854.182251643925</v>
+        <v>1595.696666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>25705.73</v>
+        <v>3954.52</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -9107,23 +9107,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12540</v>
+        <v>15304</v>
       </c>
       <c r="E15" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="F15" t="n">
-        <v>1448.267748356074</v>
+        <v>1767.483333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>9659.32</v>
+        <v>11788.35</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -9135,25 +9135,25 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3751</v>
+        <v>15304</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="F16" t="n">
-        <v>597.5669752323226</v>
+        <v>1767.483333333333</v>
       </c>
       <c r="G16" t="n">
-        <v>5702.02444921501</v>
+        <v>11788.35</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -9168,28 +9168,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1214</v>
+        <v>15304</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
-        <v>193.4352393900787</v>
+        <v>1767.483333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>1845.77212272009</v>
+        <v>11788.35</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9206,23 +9206,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3411</v>
+        <v>2792</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F18" t="n">
-        <v>543.5177853775987</v>
+        <v>444.84</v>
       </c>
       <c r="G18" t="n">
-        <v>5186.2834280649</v>
+        <v>4244.693333333334</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9234,28 +9234,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1558</v>
+        <v>2792</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>96.61</v>
+        <v>444.84</v>
       </c>
       <c r="G19" t="n">
-        <v>2822.033333333333</v>
+        <v>4244.693333333334</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9267,28 +9267,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1558</v>
+        <v>2792</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F20" t="n">
-        <v>96.61</v>
+        <v>444.84</v>
       </c>
       <c r="G20" t="n">
-        <v>2822.033333333333</v>
+        <v>4244.693333333334</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -9333,25 +9333,25 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Vacuum Cleaner -SBV-KT-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1536</v>
+        <v>1558</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>96.61</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2822.033333333333</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -9366,28 +9366,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10295</v>
+        <v>1558</v>
       </c>
       <c r="E23" t="n">
-        <v>243</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>2341.410627974398</v>
+        <v>96.61</v>
       </c>
       <c r="G23" t="n">
-        <v>17798.32</v>
+        <v>2822.033333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9399,28 +9399,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Vacuum Cleaner -SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1225</v>
+        <v>1536</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>278.6015437369471</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>2117.800000000001</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9437,23 +9437,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1666</v>
+        <v>13186</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>311</v>
       </c>
       <c r="F25" t="n">
-        <v>378.937828288655</v>
+        <v>2998.95</v>
       </c>
       <c r="G25" t="n">
-        <v>2880.510000000001</v>
+        <v>22796.63</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9606,19 +9606,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8806</v>
+        <v>11675</v>
       </c>
       <c r="E30" t="n">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="F30" t="n">
-        <v>1760.594929246651</v>
+        <v>2310.19</v>
       </c>
       <c r="G30" t="n">
-        <v>7639.84</v>
+        <v>10520.35</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9630,28 +9630,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2869</v>
+        <v>480</v>
       </c>
       <c r="E31" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>549.5950707533494</v>
+        <v>331.085</v>
       </c>
       <c r="G31" t="n">
-        <v>2880.51</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -9696,22 +9696,22 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>480</v>
+        <v>3150</v>
       </c>
       <c r="E33" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F33" t="n">
-        <v>331.085</v>
+        <v>473.76</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9729,7 +9729,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3150</v>
+        <v>15300</v>
       </c>
       <c r="E34" t="n">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="F34" t="n">
-        <v>473.76</v>
+        <v>1421.45</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9771,19 +9771,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15300</v>
+        <v>4608</v>
       </c>
       <c r="E35" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="F35" t="n">
-        <v>1421.45</v>
+        <v>3718.05</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>8388.139999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9795,28 +9795,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2793</v>
+        <v>132</v>
       </c>
       <c r="E36" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>2253.442884238937</v>
+        <v>45.72</v>
       </c>
       <c r="G36" t="n">
-        <v>5083.9</v>
+        <v>1073.163333333333</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9828,28 +9828,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1815</v>
+        <v>132</v>
       </c>
       <c r="E37" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>1464.607115761063</v>
+        <v>45.72</v>
       </c>
       <c r="G37" t="n">
-        <v>3304.24</v>
+        <v>1073.163333333333</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -9894,25 +9894,25 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>132</v>
+        <v>18333</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="F39" t="n">
-        <v>45.72</v>
+        <v>1509.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1073.163333333333</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -9927,28 +9927,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>132</v>
+        <v>64485</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>565</v>
       </c>
       <c r="F40" t="n">
-        <v>45.72</v>
+        <v>8136.71</v>
       </c>
       <c r="G40" t="n">
-        <v>1073.163333333333</v>
+        <v>15421.19</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9969,13 +9969,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18333</v>
+        <v>32742</v>
       </c>
       <c r="E41" t="n">
-        <v>125</v>
+        <v>369</v>
       </c>
       <c r="F41" t="n">
-        <v>1509.75</v>
+        <v>3857.8</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9993,7 +9993,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10002,19 +10002,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>64485</v>
+        <v>40896</v>
       </c>
       <c r="E42" t="n">
-        <v>565</v>
+        <v>341</v>
       </c>
       <c r="F42" t="n">
-        <v>8136.71</v>
+        <v>4160.74</v>
       </c>
       <c r="G42" t="n">
-        <v>15421.19</v>
+        <v>10422.03</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>32742</v>
+        <v>31189</v>
       </c>
       <c r="E43" t="n">
-        <v>369</v>
+        <v>276</v>
       </c>
       <c r="F43" t="n">
-        <v>3857.8</v>
+        <v>3002.24</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -10068,19 +10068,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>40896</v>
+        <v>28048</v>
       </c>
       <c r="E44" t="n">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="F44" t="n">
-        <v>4160.74</v>
+        <v>3309.45</v>
       </c>
       <c r="G44" t="n">
-        <v>10422.03</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -10101,13 +10101,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>31189</v>
+        <v>17592</v>
       </c>
       <c r="E45" t="n">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="F45" t="n">
-        <v>3002.24</v>
+        <v>1709.28</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10125,7 +10125,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10134,13 +10134,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>28048</v>
+        <v>11473</v>
       </c>
       <c r="E46" t="n">
-        <v>296</v>
+        <v>58</v>
       </c>
       <c r="F46" t="n">
-        <v>3309.45</v>
+        <v>837.11</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -10158,22 +10158,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>17592</v>
+        <v>2275</v>
       </c>
       <c r="E47" t="n">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>1709.28</v>
+        <v>101.2566666666667</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -10191,22 +10191,22 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11473</v>
+        <v>2275</v>
       </c>
       <c r="E48" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>837.11</v>
+        <v>101.2566666666667</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -10257,28 +10257,28 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2275</v>
+        <v>13839</v>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F50" t="n">
-        <v>101.2566666666667</v>
+        <v>1234.066666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>8783.613333333333</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -10290,28 +10290,28 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2275</v>
+        <v>13839</v>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F51" t="n">
-        <v>101.2566666666667</v>
+        <v>1234.066666666667</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>8783.613333333333</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -10328,23 +10328,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>9879</v>
+        <v>13839</v>
       </c>
       <c r="E52" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="F52" t="n">
-        <v>880.9606353345852</v>
+        <v>1234.066666666667</v>
       </c>
       <c r="G52" t="n">
-        <v>6270.340000000001</v>
+        <v>8783.613333333333</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -10356,28 +10356,28 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16020</v>
+        <v>10595</v>
       </c>
       <c r="E53" t="n">
-        <v>136</v>
+        <v>558</v>
       </c>
       <c r="F53" t="n">
-        <v>1428.540007073778</v>
+        <v>6436.919999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>10167.8</v>
+        <v>40492.94333333334</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10389,28 +10389,28 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15618</v>
+        <v>10595</v>
       </c>
       <c r="E54" t="n">
-        <v>132</v>
+        <v>558</v>
       </c>
       <c r="F54" t="n">
-        <v>1392.699357591636</v>
+        <v>6436.919999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>9912.699999999999</v>
+        <v>40492.94333333334</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10427,23 +10427,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9324</v>
+        <v>10595</v>
       </c>
       <c r="E55" t="n">
-        <v>491</v>
+        <v>558</v>
       </c>
       <c r="F55" t="n">
-        <v>5665.0472582144</v>
+        <v>6436.919999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>35637.29821211559</v>
+        <v>40492.94333333334</v>
       </c>
       <c r="H55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -10455,28 +10455,28 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7622</v>
+        <v>17</v>
       </c>
       <c r="E56" t="n">
-        <v>401</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>4631.068839889904</v>
+        <v>14.91666666666667</v>
       </c>
       <c r="G56" t="n">
-        <v>29132.81633241172</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -10488,28 +10488,28 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11788</v>
+        <v>17</v>
       </c>
       <c r="E57" t="n">
-        <v>621</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>7162.063329970279</v>
+        <v>14.91666666666667</v>
       </c>
       <c r="G57" t="n">
-        <v>45054.62621412588</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -10521,28 +10521,28 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3049</v>
+        <v>17</v>
       </c>
       <c r="E58" t="n">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>1852.580571925414</v>
+        <v>14.91666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>11654.0892413468</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10554,28 +10554,28 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
-        <v>14.91666666666667</v>
+        <v>102.7833333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2118.08</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -10587,28 +10587,28 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F60" t="n">
-        <v>14.91666666666667</v>
+        <v>102.7833333333333</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2118.08</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -10620,28 +10620,28 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F61" t="n">
-        <v>14.91666666666667</v>
+        <v>102.7833333333333</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2118.08</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -10653,28 +10653,28 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E62" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>102.7833333333333</v>
+        <v>17.92</v>
       </c>
       <c r="G62" t="n">
-        <v>2118.08</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10695,19 +10695,19 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>231</v>
+        <v>27843</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>298</v>
       </c>
       <c r="F63" t="n">
-        <v>102.7833333333333</v>
+        <v>3405.36</v>
       </c>
       <c r="G63" t="n">
-        <v>2118.08</v>
+        <v>6100</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -10719,28 +10719,28 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>231</v>
+        <v>31238</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>270</v>
       </c>
       <c r="F64" t="n">
-        <v>102.7833333333333</v>
+        <v>3325.19</v>
       </c>
       <c r="G64" t="n">
-        <v>2118.08</v>
+        <v>8641.530000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -10752,22 +10752,22 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>230</v>
+        <v>434</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
-        <v>17.92</v>
+        <v>36.77</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -10776,105 +10776,6 @@
         <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>27843</v>
-      </c>
-      <c r="E66" t="n">
-        <v>298</v>
-      </c>
-      <c r="F66" t="n">
-        <v>3405.36</v>
-      </c>
-      <c r="G66" t="n">
-        <v>6100</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>31238</v>
-      </c>
-      <c r="E67" t="n">
-        <v>270</v>
-      </c>
-      <c r="F67" t="n">
-        <v>3325.19</v>
-      </c>
-      <c r="G67" t="n">
-        <v>8641.530000000001</v>
-      </c>
-      <c r="H67" t="n">
-        <v>3</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>434</v>
-      </c>
-      <c r="E68" t="n">
-        <v>6</v>
-      </c>
-      <c r="F68" t="n">
-        <v>36.77</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
@@ -1179,7 +1179,7 @@
         <v>360</v>
       </c>
       <c r="F27" t="n">
-        <v>91893</v>
+        <v>91892</v>
       </c>
       <c r="G27" t="n">
         <v>43894.07</v>
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7928.059999999999</v>
+        <v>7917.78</v>
       </c>
       <c r="E32" t="n">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F32" t="n">
-        <v>147456</v>
+        <v>147450</v>
       </c>
       <c r="G32" t="n">
         <v>19060.2</v>
@@ -1431,7 +1431,7 @@
         <v>29</v>
       </c>
       <c r="F36" t="n">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>226</v>
       </c>
       <c r="F37" t="n">
-        <v>46474</v>
+        <v>46473</v>
       </c>
       <c r="G37" t="n">
         <v>11863.56</v>
@@ -1599,7 +1599,7 @@
         <v>36</v>
       </c>
       <c r="F42" t="n">
-        <v>7183</v>
+        <v>7181</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v>44</v>
       </c>
       <c r="F59" t="n">
-        <v>6481</v>
+        <v>6478</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>85</v>
       </c>
       <c r="F75" t="n">
-        <v>22023</v>
+        <v>22022</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3254,10 +3254,10 @@
         <v>20472</v>
       </c>
       <c r="G101" t="n">
-        <v>18753.34</v>
+        <v>17706.67</v>
       </c>
       <c r="H101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -3307,13 +3307,13 @@
         <v>314</v>
       </c>
       <c r="F103" t="n">
-        <v>73351</v>
+        <v>73350</v>
       </c>
       <c r="G103" t="n">
-        <v>10167.8</v>
+        <v>15251.7</v>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3335,7 +3335,7 @@
         <v>260</v>
       </c>
       <c r="F104" t="n">
-        <v>18537</v>
+        <v>18536</v>
       </c>
       <c r="G104" t="n">
         <v>39061.02</v>
@@ -3531,7 +3531,7 @@
         <v>379</v>
       </c>
       <c r="F111" t="n">
-        <v>88326</v>
+        <v>88321</v>
       </c>
       <c r="G111" t="n">
         <v>20819.92</v>
@@ -3615,7 +3615,7 @@
         <v>464</v>
       </c>
       <c r="F114" t="n">
-        <v>276348</v>
+        <v>276346</v>
       </c>
       <c r="G114" t="n">
         <v>10464.4</v>
@@ -3643,7 +3643,7 @@
         <v>379</v>
       </c>
       <c r="F115" t="n">
-        <v>75323</v>
+        <v>75322</v>
       </c>
       <c r="G115" t="n">
         <v>31096.59</v>
@@ -3811,7 +3811,7 @@
         <v>491</v>
       </c>
       <c r="F121" t="n">
-        <v>146884</v>
+        <v>146880</v>
       </c>
       <c r="G121" t="n">
         <v>4235.6</v>
@@ -6247,7 +6247,7 @@
         <v>139</v>
       </c>
       <c r="F208" t="n">
-        <v>35406</v>
+        <v>35405</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6275,7 +6275,7 @@
         <v>625</v>
       </c>
       <c r="F209" t="n">
-        <v>85359</v>
+        <v>85357</v>
       </c>
       <c r="G209" t="n">
         <v>7115.25</v>
@@ -6583,7 +6583,7 @@
         <v>138</v>
       </c>
       <c r="F220" t="n">
-        <v>27972</v>
+        <v>27970</v>
       </c>
       <c r="G220" t="n">
         <v>8471.200000000001</v>
@@ -6695,7 +6695,7 @@
         <v>434</v>
       </c>
       <c r="F224" t="n">
-        <v>105120</v>
+        <v>105119</v>
       </c>
       <c r="G224" t="n">
         <v>40672.02</v>
@@ -6947,7 +6947,7 @@
         <v>2</v>
       </c>
       <c r="F233" t="n">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -8487,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8678,23 +8678,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7640</v>
+        <v>2344</v>
       </c>
       <c r="E2" t="n">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>1522.8</v>
+        <v>467.1204429276933</v>
       </c>
       <c r="G2" t="n">
-        <v>8310.16</v>
+        <v>2549.15</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -8706,28 +8706,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - BM</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>5296</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="F3" t="n">
-        <v>19.89</v>
+        <v>1055.679557072307</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5761.01</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -8805,22 +8805,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - BM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>13.27666666666667</v>
+        <v>19.89</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -8904,22 +8904,22 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - Exact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>893</v>
+        <v>217</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>156.2766666666667</v>
+        <v>13.27666666666667</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -9003,25 +9003,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14556</v>
+        <v>893</v>
       </c>
       <c r="E12" t="n">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>1595.696666666667</v>
+        <v>156.2766666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>3954.52</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -9045,19 +9045,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14556</v>
+        <v>43666</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>430</v>
       </c>
       <c r="F13" t="n">
-        <v>1595.696666666667</v>
+        <v>4787.09</v>
       </c>
       <c r="G13" t="n">
-        <v>3954.52</v>
+        <v>11863.56</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -9069,28 +9069,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14556</v>
+        <v>33371</v>
       </c>
       <c r="E14" t="n">
-        <v>143</v>
+        <v>259</v>
       </c>
       <c r="F14" t="n">
-        <v>1595.696666666667</v>
+        <v>3854.182251643925</v>
       </c>
       <c r="G14" t="n">
-        <v>3954.52</v>
+        <v>25705.73</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -9107,23 +9107,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15304</v>
+        <v>12540</v>
       </c>
       <c r="E15" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="F15" t="n">
-        <v>1767.483333333333</v>
+        <v>1448.267748356074</v>
       </c>
       <c r="G15" t="n">
-        <v>11788.35</v>
+        <v>9659.32</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -9135,25 +9135,25 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15304</v>
+        <v>3751</v>
       </c>
       <c r="E16" t="n">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="F16" t="n">
-        <v>1767.483333333333</v>
+        <v>597.5669752323226</v>
       </c>
       <c r="G16" t="n">
-        <v>11788.35</v>
+        <v>5702.02444921501</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -9168,28 +9168,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15304</v>
+        <v>1214</v>
       </c>
       <c r="E17" t="n">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
-        <v>1767.483333333333</v>
+        <v>193.4352393900787</v>
       </c>
       <c r="G17" t="n">
-        <v>11788.35</v>
+        <v>1845.77212272009</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9206,23 +9206,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2792</v>
+        <v>3411</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>444.84</v>
+        <v>543.5177853775987</v>
       </c>
       <c r="G18" t="n">
-        <v>4244.693333333334</v>
+        <v>5186.2834280649</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9234,28 +9234,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2792</v>
+        <v>4674</v>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>444.84</v>
+        <v>289.83</v>
       </c>
       <c r="G19" t="n">
-        <v>4244.693333333334</v>
+        <v>8466.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9267,28 +9267,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Vacuum Cleaner -SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2792</v>
+        <v>1536</v>
       </c>
       <c r="E20" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>444.84</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>4244.693333333334</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9300,28 +9300,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1558</v>
+        <v>10295</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>243</v>
       </c>
       <c r="F21" t="n">
-        <v>96.61</v>
+        <v>2341.410627974398</v>
       </c>
       <c r="G21" t="n">
-        <v>2822.033333333333</v>
+        <v>17798.32</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9333,28 +9333,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1558</v>
+        <v>1225</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F22" t="n">
-        <v>96.61</v>
+        <v>278.6015437369471</v>
       </c>
       <c r="G22" t="n">
-        <v>2822.033333333333</v>
+        <v>2117.800000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9366,28 +9366,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1558</v>
+        <v>1666</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F23" t="n">
-        <v>96.61</v>
+        <v>378.937828288655</v>
       </c>
       <c r="G23" t="n">
-        <v>2822.033333333333</v>
+        <v>2880.510000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Vacuum Cleaner -SBV-KT-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01-Branded</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9408,13 +9408,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1536</v>
+        <v>2771</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>468.89</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9432,7 +9432,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9441,19 +9441,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13186</v>
+        <v>918</v>
       </c>
       <c r="E25" t="n">
-        <v>311</v>
+        <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>2998.95</v>
+        <v>100.5533333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>22796.63</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9465,22 +9465,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01-Branded</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2771</v>
+        <v>918</v>
       </c>
       <c r="E26" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>468.89</v>
+        <v>100.5533333333333</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -9531,28 +9531,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>918</v>
+        <v>8806</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>184</v>
       </c>
       <c r="F28" t="n">
-        <v>100.5533333333333</v>
+        <v>1760.594929246651</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>7639.84</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9573,19 +9573,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>918</v>
+        <v>2869</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>100.5533333333333</v>
+        <v>549.5950707533494</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9597,28 +9597,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11675</v>
+        <v>480</v>
       </c>
       <c r="E30" t="n">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>2310.19</v>
+        <v>331.085</v>
       </c>
       <c r="G30" t="n">
-        <v>10520.35</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -9663,22 +9663,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>480</v>
+        <v>3150</v>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F32" t="n">
-        <v>331.085</v>
+        <v>473.76</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9696,7 +9696,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9705,13 +9705,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3150</v>
+        <v>15300</v>
       </c>
       <c r="E33" t="n">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="F33" t="n">
-        <v>473.76</v>
+        <v>1421.45</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9729,7 +9729,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9738,19 +9738,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15300</v>
+        <v>2793</v>
       </c>
       <c r="E34" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F34" t="n">
-        <v>1421.45</v>
+        <v>2253.442884238937</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9767,23 +9767,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4608</v>
+        <v>1815</v>
       </c>
       <c r="E35" t="n">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="F35" t="n">
-        <v>3718.05</v>
+        <v>1464.607115761063</v>
       </c>
       <c r="G35" t="n">
-        <v>8388.139999999999</v>
+        <v>3304.24</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9804,19 +9804,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>132</v>
+        <v>396</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
-        <v>45.72</v>
+        <v>137.16</v>
       </c>
       <c r="G36" t="n">
-        <v>1073.163333333333</v>
+        <v>3219.49</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9828,25 +9828,25 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>132</v>
+        <v>18333</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="F37" t="n">
-        <v>45.72</v>
+        <v>1509.75</v>
       </c>
       <c r="G37" t="n">
-        <v>1073.163333333333</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -9861,28 +9861,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>132</v>
+        <v>64485</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>565</v>
       </c>
       <c r="F38" t="n">
-        <v>45.72</v>
+        <v>8136.71</v>
       </c>
       <c r="G38" t="n">
-        <v>1073.163333333333</v>
+        <v>15421.19</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9903,13 +9903,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18333</v>
+        <v>32742</v>
       </c>
       <c r="E39" t="n">
-        <v>125</v>
+        <v>369</v>
       </c>
       <c r="F39" t="n">
-        <v>1509.75</v>
+        <v>3857.8</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9927,7 +9927,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9936,19 +9936,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>64485</v>
+        <v>40896</v>
       </c>
       <c r="E40" t="n">
-        <v>565</v>
+        <v>341</v>
       </c>
       <c r="F40" t="n">
-        <v>8136.71</v>
+        <v>4160.74</v>
       </c>
       <c r="G40" t="n">
-        <v>15421.19</v>
+        <v>10422.03</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9969,13 +9969,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32742</v>
+        <v>31189</v>
       </c>
       <c r="E41" t="n">
-        <v>369</v>
+        <v>276</v>
       </c>
       <c r="F41" t="n">
-        <v>3857.8</v>
+        <v>3002.24</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9993,7 +9993,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10002,19 +10002,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>40896</v>
+        <v>28048</v>
       </c>
       <c r="E42" t="n">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="F42" t="n">
-        <v>4160.74</v>
+        <v>3309.45</v>
       </c>
       <c r="G42" t="n">
-        <v>10422.03</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>31189</v>
+        <v>17592</v>
       </c>
       <c r="E43" t="n">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="F43" t="n">
-        <v>3002.24</v>
+        <v>1709.28</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -10068,13 +10068,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28048</v>
+        <v>11473</v>
       </c>
       <c r="E44" t="n">
-        <v>296</v>
+        <v>58</v>
       </c>
       <c r="F44" t="n">
-        <v>3309.45</v>
+        <v>837.11</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -10092,22 +10092,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17592</v>
+        <v>2275</v>
       </c>
       <c r="E45" t="n">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>1709.28</v>
+        <v>101.2566666666667</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10125,22 +10125,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11473</v>
+        <v>2275</v>
       </c>
       <c r="E46" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="F46" t="n">
-        <v>837.11</v>
+        <v>101.2566666666667</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -10191,7 +10191,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10200,19 +10200,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2275</v>
+        <v>9879</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="F48" t="n">
-        <v>101.2566666666667</v>
+        <v>880.9606353345852</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>6270.340000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10224,28 +10224,28 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2275</v>
+        <v>16019</v>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="F49" t="n">
-        <v>101.2566666666667</v>
+        <v>1428.540007073778</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>10167.8</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -10262,20 +10262,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13839</v>
+        <v>15618</v>
       </c>
       <c r="E50" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F50" t="n">
-        <v>1234.066666666667</v>
+        <v>1392.699357591636</v>
       </c>
       <c r="G50" t="n">
-        <v>8783.613333333333</v>
+        <v>9912.699999999999</v>
       </c>
       <c r="H50" t="n">
         <v>2</v>
@@ -10290,28 +10290,28 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13839</v>
+        <v>10104</v>
       </c>
       <c r="E51" t="n">
-        <v>117</v>
+        <v>532</v>
       </c>
       <c r="F51" t="n">
-        <v>1234.066666666667</v>
+        <v>6138.849815939053</v>
       </c>
       <c r="G51" t="n">
-        <v>8783.613333333333</v>
+        <v>38617.86347020995</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -10323,28 +10323,28 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13839</v>
+        <v>7358</v>
       </c>
       <c r="E52" t="n">
-        <v>117</v>
+        <v>388</v>
       </c>
       <c r="F52" t="n">
-        <v>1234.066666666667</v>
+        <v>4470.270184454361</v>
       </c>
       <c r="G52" t="n">
-        <v>8783.613333333333</v>
+        <v>28121.27496749999</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -10361,20 +10361,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10595</v>
+        <v>11379</v>
       </c>
       <c r="E53" t="n">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="F53" t="n">
-        <v>6436.919999999999</v>
+        <v>6913.384203526803</v>
       </c>
       <c r="G53" t="n">
-        <v>40492.94333333334</v>
+        <v>43490.25229379465</v>
       </c>
       <c r="H53" t="n">
         <v>11</v>
@@ -10394,23 +10394,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10595</v>
+        <v>2943</v>
       </c>
       <c r="E54" t="n">
-        <v>558</v>
+        <v>155</v>
       </c>
       <c r="F54" t="n">
-        <v>6436.919999999999</v>
+        <v>1788.255796079781</v>
       </c>
       <c r="G54" t="n">
-        <v>40492.94333333334</v>
+        <v>11249.43926849541</v>
       </c>
       <c r="H54" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10422,28 +10422,28 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10595</v>
+        <v>17</v>
       </c>
       <c r="E55" t="n">
-        <v>558</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>6436.919999999999</v>
+        <v>14.91666666666667</v>
       </c>
       <c r="G55" t="n">
-        <v>40492.94333333334</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -10521,28 +10521,28 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>693</v>
       </c>
       <c r="E58" t="n">
+        <v>19</v>
+      </c>
+      <c r="F58" t="n">
+        <v>308.35</v>
+      </c>
+      <c r="G58" t="n">
+        <v>6354.24</v>
+      </c>
+      <c r="H58" t="n">
         <v>2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>14.91666666666667</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10554,28 +10554,28 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>102.7833333333333</v>
+        <v>17.92</v>
       </c>
       <c r="G59" t="n">
-        <v>2118.08</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -10587,28 +10587,28 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>231</v>
+        <v>27843</v>
       </c>
       <c r="E60" t="n">
-        <v>6</v>
+        <v>298</v>
       </c>
       <c r="F60" t="n">
-        <v>102.7833333333333</v>
+        <v>3405.36</v>
       </c>
       <c r="G60" t="n">
-        <v>2118.08</v>
+        <v>6100</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -10620,28 +10620,28 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>231</v>
+        <v>31238</v>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>270</v>
       </c>
       <c r="F61" t="n">
-        <v>102.7833333333333</v>
+        <v>3325.19</v>
       </c>
       <c r="G61" t="n">
-        <v>2118.08</v>
+        <v>8641.530000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -10653,22 +10653,22 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>230</v>
+        <v>434</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F62" t="n">
-        <v>17.92</v>
+        <v>36.77</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -10677,105 +10677,6 @@
         <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>27843</v>
-      </c>
-      <c r="E63" t="n">
-        <v>298</v>
-      </c>
-      <c r="F63" t="n">
-        <v>3405.36</v>
-      </c>
-      <c r="G63" t="n">
-        <v>6100</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>31238</v>
-      </c>
-      <c r="E64" t="n">
-        <v>270</v>
-      </c>
-      <c r="F64" t="n">
-        <v>3325.19</v>
-      </c>
-      <c r="G64" t="n">
-        <v>8641.530000000001</v>
-      </c>
-      <c r="H64" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>434</v>
-      </c>
-      <c r="E65" t="n">
-        <v>6</v>
-      </c>
-      <c r="F65" t="n">
-        <v>36.77</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week25.xlsx
@@ -1179,13 +1179,13 @@
         <v>360</v>
       </c>
       <c r="F27" t="n">
-        <v>91892</v>
+        <v>91890</v>
       </c>
       <c r="G27" t="n">
-        <v>43894.07</v>
+        <v>55757.63</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -2893,7 +2893,7 @@
         <v>4320.34</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -3189,13 +3189,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1389.31</v>
+        <v>1378.34</v>
       </c>
       <c r="E99" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F99" t="n">
-        <v>55741</v>
+        <v>55740</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>379</v>
       </c>
       <c r="F111" t="n">
-        <v>88321</v>
+        <v>88320</v>
       </c>
       <c r="G111" t="n">
         <v>20819.92</v>
@@ -3643,7 +3643,7 @@
         <v>379</v>
       </c>
       <c r="F115" t="n">
-        <v>75322</v>
+        <v>75321</v>
       </c>
       <c r="G115" t="n">
         <v>31096.59</v>
@@ -3755,7 +3755,7 @@
         <v>110</v>
       </c>
       <c r="F119" t="n">
-        <v>12438</v>
+        <v>12436</v>
       </c>
       <c r="G119" t="n">
         <v>2856.19</v>
@@ -3811,7 +3811,7 @@
         <v>491</v>
       </c>
       <c r="F121" t="n">
-        <v>146880</v>
+        <v>146877</v>
       </c>
       <c r="G121" t="n">
         <v>4235.6</v>
@@ -3979,7 +3979,7 @@
         <v>122</v>
       </c>
       <c r="F127" t="n">
-        <v>8751</v>
+        <v>8750</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4147,7 +4147,7 @@
         <v>13</v>
       </c>
       <c r="F133" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G133" t="n">
         <v>1332.38</v>
@@ -4371,7 +4371,7 @@
         <v>16</v>
       </c>
       <c r="F141" t="n">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="G141" t="n">
         <v>1380</v>
@@ -5519,7 +5519,7 @@
         <v>11</v>
       </c>
       <c r="F182" t="n">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="G182" t="n">
         <v>630.5</v>
@@ -5662,10 +5662,10 @@
         <v>34183</v>
       </c>
       <c r="G187" t="n">
-        <v>39741.51</v>
+        <v>40079.65</v>
       </c>
       <c r="H187" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -6138,10 +6138,10 @@
         <v>1134</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>10168.64</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -6247,7 +6247,7 @@
         <v>139</v>
       </c>
       <c r="F208" t="n">
-        <v>35405</v>
+        <v>35403</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>1143</v>
       </c>
       <c r="F218" t="n">
-        <v>141956</v>
+        <v>141951</v>
       </c>
       <c r="G218" t="n">
         <v>5761.01</v>
@@ -6583,7 +6583,7 @@
         <v>138</v>
       </c>
       <c r="F220" t="n">
-        <v>27970</v>
+        <v>27969</v>
       </c>
       <c r="G220" t="n">
         <v>8471.200000000001</v>
@@ -8619,7 +8619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9239,23 +9239,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4674</v>
+        <v>1558</v>
       </c>
       <c r="E19" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>289.83</v>
+        <v>96.61</v>
       </c>
       <c r="G19" t="n">
-        <v>8466.1</v>
+        <v>2822.033333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9267,25 +9267,25 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Vacuum Cleaner -SBV-KT-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1536</v>
+        <v>1558</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>96.61</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2822.033333333333</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -9300,28 +9300,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10295</v>
+        <v>1558</v>
       </c>
       <c r="E21" t="n">
-        <v>243</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>2341.410627974398</v>
+        <v>96.61</v>
       </c>
       <c r="G21" t="n">
-        <v>17798.32</v>
+        <v>2822.033333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9333,28 +9333,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Vacuum Cleaner -SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1225</v>
+        <v>1536</v>
       </c>
       <c r="E22" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>278.6015437369471</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>2117.800000000001</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9371,23 +9371,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1666</v>
+        <v>10295</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>243</v>
       </c>
       <c r="F23" t="n">
-        <v>378.937828288655</v>
+        <v>2341.410627974398</v>
       </c>
       <c r="G23" t="n">
-        <v>2880.510000000001</v>
+        <v>17798.32</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9399,28 +9399,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01-Branded</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2771</v>
+        <v>1225</v>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>468.89</v>
+        <v>278.6015437369471</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2117.800000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9432,28 +9432,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>918</v>
+        <v>1666</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>100.5533333333333</v>
+        <v>378.937828288655</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2880.510000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9465,22 +9465,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01-Branded</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>918</v>
+        <v>2771</v>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F26" t="n">
-        <v>100.5533333333333</v>
+        <v>468.89</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -9531,28 +9531,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8806</v>
+        <v>918</v>
       </c>
       <c r="E28" t="n">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>1760.594929246651</v>
+        <v>100.5533333333333</v>
       </c>
       <c r="G28" t="n">
-        <v>7639.84</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9573,19 +9573,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2869</v>
+        <v>918</v>
       </c>
       <c r="E29" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>549.5950707533494</v>
+        <v>100.5533333333333</v>
       </c>
       <c r="G29" t="n">
-        <v>2880.51</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9597,28 +9597,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>480</v>
+        <v>8806</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="F30" t="n">
-        <v>331.085</v>
+        <v>1760.594929246651</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>7639.84</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9630,28 +9630,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>480</v>
+        <v>2869</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>331.085</v>
+        <v>549.5950707533494</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9663,22 +9663,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3150</v>
+        <v>480</v>
       </c>
       <c r="E32" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>473.76</v>
+        <v>331.085</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9696,22 +9696,22 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15300</v>
+        <v>480</v>
       </c>
       <c r="E33" t="n">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>1421.45</v>
+        <v>331.085</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9729,7 +9729,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9738,19 +9738,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2793</v>
+        <v>3150</v>
       </c>
       <c r="E34" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="F34" t="n">
-        <v>2253.442884238937</v>
+        <v>473.76</v>
       </c>
       <c r="G34" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9762,28 +9762,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1815</v>
+        <v>15300</v>
       </c>
       <c r="E35" t="n">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F35" t="n">
-        <v>1464.607115761063</v>
+        <v>1421.45</v>
       </c>
       <c r="G35" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9795,25 +9795,25 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>396</v>
+        <v>2793</v>
       </c>
       <c r="E36" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="F36" t="n">
-        <v>137.16</v>
+        <v>2253.442884238937</v>
       </c>
       <c r="G36" t="n">
-        <v>3219.49</v>
+        <v>5083.9</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -9828,28 +9828,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>18333</v>
+        <v>1815</v>
       </c>
       <c r="E37" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="F37" t="n">
-        <v>1509.75</v>
+        <v>1464.607115761063</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9861,28 +9861,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>64485</v>
+        <v>132</v>
       </c>
       <c r="E38" t="n">
-        <v>565</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>8136.71</v>
+        <v>45.72</v>
       </c>
       <c r="G38" t="n">
-        <v>15421.19</v>
+        <v>1073.163333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -9894,25 +9894,25 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>32742</v>
+        <v>132</v>
       </c>
       <c r="E39" t="n">
-        <v>369</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>3857.8</v>
+        <v>45.72</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1073.163333333333</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -9927,28 +9927,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40896</v>
+        <v>132</v>
       </c>
       <c r="E40" t="n">
-        <v>341</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>4160.74</v>
+        <v>45.72</v>
       </c>
       <c r="G40" t="n">
-        <v>10422.03</v>
+        <v>1073.163333333333</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9969,13 +9969,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31189</v>
+        <v>18333</v>
       </c>
       <c r="E41" t="n">
-        <v>276</v>
+        <v>125</v>
       </c>
       <c r="F41" t="n">
-        <v>3002.24</v>
+        <v>1509.75</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9993,7 +9993,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10002,19 +10002,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28048</v>
+        <v>64485</v>
       </c>
       <c r="E42" t="n">
-        <v>296</v>
+        <v>565</v>
       </c>
       <c r="F42" t="n">
-        <v>3309.45</v>
+        <v>8136.71</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>15421.19</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17592</v>
+        <v>32742</v>
       </c>
       <c r="E43" t="n">
-        <v>133</v>
+        <v>369</v>
       </c>
       <c r="F43" t="n">
-        <v>1709.28</v>
+        <v>3857.8</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -10068,19 +10068,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11473</v>
+        <v>40896</v>
       </c>
       <c r="E44" t="n">
-        <v>58</v>
+        <v>341</v>
       </c>
       <c r="F44" t="n">
-        <v>837.11</v>
+        <v>4160.74</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>10422.03</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10092,22 +10092,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2275</v>
+        <v>31189</v>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>276</v>
       </c>
       <c r="F45" t="n">
-        <v>101.2566666666667</v>
+        <v>3002.24</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10125,22 +10125,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2275</v>
+        <v>28048</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>296</v>
       </c>
       <c r="F46" t="n">
-        <v>101.2566666666667</v>
+        <v>3309.45</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -10158,22 +10158,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2275</v>
+        <v>17591</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="F47" t="n">
-        <v>101.2566666666667</v>
+        <v>1709.28</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -10191,28 +10191,28 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>9879</v>
+        <v>11473</v>
       </c>
       <c r="E48" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="F48" t="n">
-        <v>880.9606353345852</v>
+        <v>837.11</v>
       </c>
       <c r="G48" t="n">
-        <v>6270.340000000001</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10224,28 +10224,28 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16019</v>
+        <v>2275</v>
       </c>
       <c r="E49" t="n">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>1428.540007073778</v>
+        <v>101.2566666666667</v>
       </c>
       <c r="G49" t="n">
-        <v>10167.8</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -10257,28 +10257,28 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15618</v>
+        <v>2275</v>
       </c>
       <c r="E50" t="n">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>1392.699357591636</v>
+        <v>101.2566666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>9912.699999999999</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -10290,28 +10290,28 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10104</v>
+        <v>2275</v>
       </c>
       <c r="E51" t="n">
-        <v>532</v>
+        <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>6138.849815939053</v>
+        <v>101.2566666666667</v>
       </c>
       <c r="G51" t="n">
-        <v>38617.86347020995</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -10323,28 +10323,28 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7358</v>
+        <v>9879</v>
       </c>
       <c r="E52" t="n">
-        <v>388</v>
+        <v>84</v>
       </c>
       <c r="F52" t="n">
-        <v>4470.270184454361</v>
+        <v>880.9606353345852</v>
       </c>
       <c r="G52" t="n">
-        <v>28121.27496749999</v>
+        <v>6270.340000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -10356,28 +10356,28 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11379</v>
+        <v>16019</v>
       </c>
       <c r="E53" t="n">
-        <v>599</v>
+        <v>136</v>
       </c>
       <c r="F53" t="n">
-        <v>6913.384203526803</v>
+        <v>1428.540007073778</v>
       </c>
       <c r="G53" t="n">
-        <v>43490.25229379465</v>
+        <v>10167.8</v>
       </c>
       <c r="H53" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10389,28 +10389,28 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2943</v>
+        <v>15618</v>
       </c>
       <c r="E54" t="n">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="F54" t="n">
-        <v>1788.255796079781</v>
+        <v>1392.699357591636</v>
       </c>
       <c r="G54" t="n">
-        <v>11249.43926849541</v>
+        <v>9912.699999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10431,19 +10431,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>10104</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>532</v>
       </c>
       <c r="F55" t="n">
-        <v>14.91666666666667</v>
+        <v>6138.849815939053</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>39668.27438701584</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -10464,19 +10464,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>7358</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>388</v>
       </c>
       <c r="F56" t="n">
-        <v>14.91666666666667</v>
+        <v>4470.270184454361</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>28886.17730973206</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -10497,19 +10497,19 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>17</v>
+        <v>11379</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>599</v>
       </c>
       <c r="F57" t="n">
-        <v>14.91666666666667</v>
+        <v>6913.384203526803</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>44673.19282128613</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -10521,28 +10521,28 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>693</v>
+        <v>2943</v>
       </c>
       <c r="E58" t="n">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="F58" t="n">
-        <v>308.35</v>
+        <v>1788.255796079781</v>
       </c>
       <c r="G58" t="n">
-        <v>6354.24</v>
+        <v>11555.42548196596</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10554,22 +10554,22 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>230</v>
+        <v>17</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>17.92</v>
+        <v>14.91666666666667</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -10587,28 +10587,28 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>27843</v>
+        <v>17</v>
       </c>
       <c r="E60" t="n">
-        <v>298</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>3405.36</v>
+        <v>14.91666666666667</v>
       </c>
       <c r="G60" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -10620,28 +10620,28 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>31238</v>
+        <v>17</v>
       </c>
       <c r="E61" t="n">
-        <v>270</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>3325.19</v>
+        <v>14.91666666666667</v>
       </c>
       <c r="G61" t="n">
-        <v>8641.530000000001</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -10653,30 +10653,162 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>693</v>
+      </c>
+      <c r="E62" t="n">
+        <v>19</v>
+      </c>
+      <c r="F62" t="n">
+        <v>308.35</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6354.24</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>230</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>B0D2LJSQXZ</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>27843</v>
+      </c>
+      <c r="E64" t="n">
+        <v>298</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3405.36</v>
+      </c>
+      <c r="G64" t="n">
+        <v>6100</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>31238</v>
+      </c>
+      <c r="E65" t="n">
+        <v>270</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3325.19</v>
+      </c>
+      <c r="G65" t="n">
+        <v>8641.530000000001</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D66" t="n">
         <v>434</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E66" t="n">
         <v>6</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F66" t="n">
         <v>36.77</v>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>
